--- a/Assets/9.Excel/아이템 스펙.xlsx
+++ b/Assets/9.Excel/아이템 스펙.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\201\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Peace-Dungeon\Peace-Dungeon\Assets\9.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="음식" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="174">
   <si>
     <t>아이디</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -685,6 +685,42 @@
   </si>
   <si>
     <t>마나 30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다람쥐가죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛바랜돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튼튼한 나무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사슴뿔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은밀한 광석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불길한 가루</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맑은샘물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사슴눈물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1365,10 +1401,16 @@
       <c r="B24">
         <v>6523</v>
       </c>
+      <c r="C24" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>6524</v>
+      </c>
+      <c r="C25" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
@@ -1624,35 +1666,54 @@
       <c r="B15">
         <v>8014</v>
       </c>
+      <c r="C15" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>8015</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>8016</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>8017</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>8018</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>8019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2249,6 +2310,9 @@
       <c r="B41">
         <v>7040</v>
       </c>
+      <c r="C41" t="s">
+        <v>165</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
